--- a/output/Hubei/荆门市_api_news.xlsx
+++ b/output/Hubei/荆门市_api_news.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -565,14 +565,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -592,32 +590,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>地区生产总值发展速度</t>
+          <t>统一地址查询服务根据地址搜索接口</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>经济建设</t>
+          <t>地理空间</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>地区生产总值发展速度</t>
+          <t>统一地址查询服务根据地址搜索接口</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>东宝区</t>
+          <t>市公安局</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -639,17 +637,15 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>/irsp</t>
+          <t>/ybss</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -666,32 +662,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>统一地址查询服务根据地址搜索接口</t>
+          <t>地区生产总值发展速度</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>地理空间</t>
+          <t>经济建设</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>统一地址查询服务根据地址搜索接口</t>
+          <t>地区生产总值发展速度</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>市公安局</t>
+          <t>东宝区</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -716,14 +712,12 @@
         <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>/ybss</t>
+          <t>/irsp</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -740,22 +734,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>人员从业情况</t>
+          <t>高中学校查询</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>教育文化</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>人员从业情况</t>
+          <t>高中学校查询</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>市文化旅游局</t>
+          <t>市教育局</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -765,7 +759,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -787,14 +781,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -814,22 +806,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>高中学校查询</t>
+          <t>人员从业情况</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>教育文化</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>高中学校查询</t>
+          <t>人员从业情况</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>市教育局</t>
+          <t>市文化旅游局</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -861,14 +853,12 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -940,9 +930,7 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1014,9 +1002,7 @@
       <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1088,9 +1074,7 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1110,7 +1094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>互联网上网服务营业场所</t>
+          <t>小学学校信息查询</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1120,12 +1104,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>互联网上网服务营业场所</t>
+          <t>小学学校信息查询</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>市文化旅游局</t>
+          <t>市教育局</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1135,7 +1119,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1162,9 +1146,7 @@
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1184,7 +1166,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小学学校信息查询</t>
+          <t>互联网上网服务营业场所</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1194,12 +1176,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>小学学校信息查询</t>
+          <t>互联网上网服务营业场所</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>市教育局</t>
+          <t>市文化旅游局</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1209,7 +1191,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1231,14 +1213,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1310,9 +1290,7 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1384,9 +1362,7 @@
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1406,22 +1382,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>荆门市公交线路列表</t>
+          <t>特殊学校查询</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>教育文化</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>荆门市公交线路列表</t>
+          <t>特殊学校查询</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>市交通运输局</t>
+          <t>市教育局</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1431,7 +1407,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1458,9 +1434,7 @@
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1480,7 +1454,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>道路货物运输企业基本信息</t>
+          <t>荆门市公交线路列表</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1490,7 +1464,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>道路货物运输企业基本信息</t>
+          <t>荆门市公交线路列表</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1532,9 +1506,7 @@
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1554,7 +1526,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>荆门市公交线路站点列表</t>
+          <t>道路货物运输企业基本信息</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1564,7 +1536,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>荆门市公交线路站点列表</t>
+          <t>道路货物运输企业基本信息</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1606,9 +1578,7 @@
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1628,7 +1598,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>出租汽车企业基本信息</t>
+          <t>荆门市公交线路站点列表</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1638,7 +1608,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>出租汽车企业基本信息</t>
+          <t>荆门市公交线路站点列表</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1680,9 +1650,7 @@
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1702,22 +1670,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>外贸情况</t>
+          <t>出租汽车企业基本信息</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>外贸情况</t>
+          <t>出租汽车企业基本信息</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>市文化旅游局</t>
+          <t>市交通运输局</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1754,9 +1722,7 @@
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1776,22 +1742,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>特殊学校查询</t>
+          <t>外贸情况</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>教育文化</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>特殊学校查询</t>
+          <t>外贸情况</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>市教育局</t>
+          <t>市文化旅游局</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1823,14 +1789,12 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1902,9 +1866,7 @@
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -1976,9 +1938,7 @@
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -2050,9 +2010,7 @@
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>/irsp</t>
@@ -2124,9 +2082,7 @@
       <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>/irsp</t>
